--- a/docs/workbook-split/dateien/Stundensätze.xlsx
+++ b/docs/workbook-split/dateien/Stundensätze.xlsx
@@ -724,21 +724,17 @@
           <t>Mitarbeiter</t>
         </is>
       </c>
-      <c r="H7" s="7">
-        <f>SUMIFS($F$65:$F$76,$C$65:$C$76,"West")</f>
-        <v/>
-      </c>
-      <c r="I7" s="7">
-        <f>SUMIFS($F$65:$F$76,$C$65:$C$76,"Süd-West")</f>
-        <v/>
-      </c>
-      <c r="J7" s="7">
-        <f>SUMIFS($F$65:$F$76,$C$65:$C$76,"Ost")</f>
-        <v/>
-      </c>
-      <c r="K7" s="7">
-        <f>SUMIFS($F$65:$F$76,$C$65:$C$76,"Berlin")</f>
-        <v/>
+      <c r="H7" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="I7" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="J7" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="K7" s="7" t="n">
+        <v>3</v>
       </c>
       <c r="L7" s="1" t="n"/>
       <c r="M7" s="1" t="n"/>
@@ -764,21 +760,17 @@
           <t>Bezahlte Stunden</t>
         </is>
       </c>
-      <c r="H8" s="7">
-        <f>SUMIFS($H$65:$H$76,$C$65:$C$76,"West")</f>
-        <v/>
-      </c>
-      <c r="I8" s="7">
-        <f>SUMIFS($H$65:$H$76,$C$65:$C$76,"Süd-West")</f>
-        <v/>
-      </c>
-      <c r="J8" s="7">
-        <f>SUMIFS($H$65:$H$76,$C$65:$C$76,"Ost")</f>
-        <v/>
-      </c>
-      <c r="K8" s="7">
-        <f>SUMIFS($H$65:$H$76,$C$65:$C$76,"Berlin")</f>
-        <v/>
+      <c r="H8" s="7" t="n">
+        <v>22836</v>
+      </c>
+      <c r="I8" s="7" t="n">
+        <v>26352</v>
+      </c>
+      <c r="J8" s="7" t="n">
+        <v>22836</v>
+      </c>
+      <c r="K8" s="7" t="n">
+        <v>6228</v>
       </c>
       <c r="L8" s="1" t="n"/>
       <c r="M8" s="1" t="n"/>
@@ -804,21 +796,17 @@
           <t>Produktive Stunden</t>
         </is>
       </c>
-      <c r="H9" s="7">
-        <f>H8*$D$25</f>
-        <v/>
-      </c>
-      <c r="I9" s="7">
-        <f>I8*$D$25</f>
-        <v/>
-      </c>
-      <c r="J9" s="7">
-        <f>J8*$D$25</f>
-        <v/>
-      </c>
-      <c r="K9" s="7">
-        <f>K8*$D$25</f>
-        <v/>
+      <c r="H9" s="7" t="n">
+        <v>14812.54054054054</v>
+      </c>
+      <c r="I9" s="7" t="n">
+        <v>17093.18918918919</v>
+      </c>
+      <c r="J9" s="7" t="n">
+        <v>14812.54054054054</v>
+      </c>
+      <c r="K9" s="7" t="n">
+        <v>4039.783783783784</v>
       </c>
       <c r="L9" s="1" t="n"/>
       <c r="M9" s="1" t="n"/>
@@ -844,21 +832,17 @@
           <t>Direktlohn inkl. Tarif</t>
         </is>
       </c>
-      <c r="H10" s="8">
-        <f>SUMIFS($I$65:$I$76,$C$65:$C$76,"West")*(1+$D$20)^('[Steuerung.xlsx]Steuerung'!$F$11-$D$22)</f>
-        <v/>
-      </c>
-      <c r="I10" s="8">
-        <f>SUMIFS($I$65:$I$76,$C$65:$C$76,"Süd-West")*(1+$D$20)^('[Steuerung.xlsx]Steuerung'!$F$11-$D$22)</f>
-        <v/>
-      </c>
-      <c r="J10" s="8">
-        <f>SUMIFS($I$65:$I$76,$C$65:$C$76,"Ost")*(1+$D$20)^('[Steuerung.xlsx]Steuerung'!$F$11-$D$22)</f>
-        <v/>
-      </c>
-      <c r="K10" s="8">
-        <f>SUMIFS($I$65:$I$76,$C$65:$C$76,"Berlin")*(1+$D$20)^('[Steuerung.xlsx]Steuerung'!$F$11-$D$22)</f>
-        <v/>
+      <c r="H10" s="8" t="n">
+        <v>512326.6968</v>
+      </c>
+      <c r="I10" s="8" t="n">
+        <v>494067.7632</v>
+      </c>
+      <c r="J10" s="8" t="n">
+        <v>455899.9596</v>
+      </c>
+      <c r="K10" s="8" t="n">
+        <v>119613.9</v>
       </c>
       <c r="L10" s="1" t="n"/>
       <c r="M10" s="1" t="n"/>
@@ -884,21 +868,17 @@
           <t>Bruttolohn mit Zuschlägen</t>
         </is>
       </c>
-      <c r="H11" s="7">
-        <f>H10*(1+$D$13+$D$14)</f>
-        <v/>
-      </c>
-      <c r="I11" s="7">
-        <f>I10*(1+$D$13+$D$14)</f>
-        <v/>
-      </c>
-      <c r="J11" s="7">
-        <f>J10*(1+$D$13+$D$14)</f>
-        <v/>
-      </c>
-      <c r="K11" s="7">
-        <f>K10*(1+$D$13+$D$14)</f>
-        <v/>
+      <c r="H11" s="7" t="n">
+        <v>556233.09471576</v>
+      </c>
+      <c r="I11" s="7" t="n">
+        <v>536409.3705062399</v>
+      </c>
+      <c r="J11" s="7" t="n">
+        <v>494970.58613772</v>
+      </c>
+      <c r="K11" s="7" t="n">
+        <v>129864.81123</v>
       </c>
       <c r="L11" s="1" t="n"/>
       <c r="M11" s="1" t="n"/>
@@ -924,21 +904,17 @@
           <t>Personalkosten gesamt</t>
         </is>
       </c>
-      <c r="H12" s="8">
-        <f>H11*(1+$D$15+$D$16+$D$17)+H7*($D$18+$D$19)*(1+$D$21)^('[Steuerung.xlsx]Steuerung'!$F$11-$D$22)</f>
-        <v/>
-      </c>
-      <c r="I12" s="8">
-        <f>I11*(1+$D$15+$D$16+$D$17)+I7*($D$18+$D$19)*(1+$D$21)^('[Steuerung.xlsx]Steuerung'!$F$11-$D$22)</f>
-        <v/>
-      </c>
-      <c r="J12" s="8">
-        <f>J11*(1+$D$15+$D$16+$D$17)+J7*($D$18+$D$19)*(1+$D$21)^('[Steuerung.xlsx]Steuerung'!$F$11-$D$22)</f>
-        <v/>
-      </c>
-      <c r="K12" s="8">
-        <f>K11*(1+$D$15+$D$16+$D$17)+K7*($D$18+$D$19)*(1+$D$21)^('[Steuerung.xlsx]Steuerung'!$F$11-$D$22)</f>
-        <v/>
+      <c r="H12" s="8" t="n">
+        <v>703580.8210599041</v>
+      </c>
+      <c r="I12" s="8" t="n">
+        <v>681193.6593702174</v>
+      </c>
+      <c r="J12" s="8" t="n">
+        <v>626831.1503133356</v>
+      </c>
+      <c r="K12" s="8" t="n">
+        <v>164530.635508944</v>
       </c>
       <c r="L12" s="1" t="n"/>
       <c r="M12" s="1" t="n"/>
@@ -964,21 +940,17 @@
           <t>Kostensatz EUR / Std.</t>
         </is>
       </c>
-      <c r="H13" s="7">
-        <f>IF(H9=0,"n.a.",H12/H9)</f>
-        <v/>
-      </c>
-      <c r="I13" s="7">
-        <f>IF(I9=0,"n.a.",I12/I9)</f>
-        <v/>
-      </c>
-      <c r="J13" s="7">
-        <f>IF(J9=0,"n.a.",J12/J9)</f>
-        <v/>
-      </c>
-      <c r="K13" s="7">
-        <f>IF(K9=0,"n.a.",K12/K9)</f>
-        <v/>
+      <c r="H13" s="7" t="n">
+        <v>47.49899715948584</v>
+      </c>
+      <c r="I13" s="7" t="n">
+        <v>39.85175919079204</v>
+      </c>
+      <c r="J13" s="7" t="n">
+        <v>42.3175989694514</v>
+      </c>
+      <c r="K13" s="7" t="n">
+        <v>40.72758452306068</v>
       </c>
       <c r="L13" s="1" t="n"/>
       <c r="M13" s="1" t="n"/>
@@ -1004,21 +976,17 @@
           <t>Personalplan</t>
         </is>
       </c>
-      <c r="H14" s="8">
-        <f>SUMIFS('[Referenzen.xlsx]Referenzen'!$C$176:$C$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,'[Steuerung.xlsx]Steuerung'!$F$11,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,"Personalaufwand")</f>
-        <v/>
-      </c>
-      <c r="I14" s="8">
-        <f>SUMIFS('[Referenzen.xlsx]Referenzen'!$D$176:$D$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,'[Steuerung.xlsx]Steuerung'!$F$11,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,"Personalaufwand")</f>
-        <v/>
-      </c>
-      <c r="J14" s="8">
-        <f>SUMIFS('[Referenzen.xlsx]Referenzen'!$E$176:$E$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,'[Steuerung.xlsx]Steuerung'!$F$11,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,"Personalaufwand")</f>
-        <v/>
-      </c>
-      <c r="K14" s="8">
-        <f>SUMIFS('[Referenzen.xlsx]Referenzen'!$F$176:$F$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,'[Steuerung.xlsx]Steuerung'!$F$11,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,"Personalaufwand")</f>
-        <v/>
+      <c r="H14" s="8" t="n">
+        <v>1785000</v>
+      </c>
+      <c r="I14" s="8" t="n">
+        <v>1100000</v>
+      </c>
+      <c r="J14" s="8" t="n">
+        <v>1121000</v>
+      </c>
+      <c r="K14" s="8" t="n">
+        <v>390000</v>
       </c>
       <c r="L14" s="1" t="n"/>
       <c r="M14" s="1" t="n"/>
@@ -1044,21 +1012,17 @@
           <t>Overhead Personal</t>
         </is>
       </c>
-      <c r="H15" s="7">
-        <f>H14-H12</f>
-        <v/>
-      </c>
-      <c r="I15" s="7">
-        <f>I14-I12</f>
-        <v/>
-      </c>
-      <c r="J15" s="7">
-        <f>J14-J12</f>
-        <v/>
-      </c>
-      <c r="K15" s="7">
-        <f>K14-K12</f>
-        <v/>
+      <c r="H15" s="7" t="n">
+        <v>1081419.178940096</v>
+      </c>
+      <c r="I15" s="7" t="n">
+        <v>418806.3406297826</v>
+      </c>
+      <c r="J15" s="7" t="n">
+        <v>494168.8496866644</v>
+      </c>
+      <c r="K15" s="7" t="n">
+        <v>225469.364491056</v>
       </c>
       <c r="L15" s="1" t="n"/>
       <c r="M15" s="1" t="n"/>
@@ -1084,21 +1048,17 @@
           <t>Übrige Gemeinkosten</t>
         </is>
       </c>
-      <c r="H16" s="8">
-        <f>SUMIFS('[Referenzen.xlsx]Referenzen'!$C$176:$C$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,'[Steuerung.xlsx]Steuerung'!$F$11,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,"Raumkosten")+SUMIFS('[Referenzen.xlsx]Referenzen'!$C$176:$C$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,'[Steuerung.xlsx]Steuerung'!$F$11,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,"Fuhrparkkosten")+SUMIFS('[Referenzen.xlsx]Referenzen'!$C$176:$C$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,'[Steuerung.xlsx]Steuerung'!$F$11,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,"Instandh. Betriebsausstattung")+SUMIFS('[Referenzen.xlsx]Referenzen'!$C$176:$C$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,'[Steuerung.xlsx]Steuerung'!$F$11,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,"Vertriebskosten")+SUMIFS('[Referenzen.xlsx]Referenzen'!$C$176:$C$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,'[Steuerung.xlsx]Steuerung'!$F$11,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,"Verwaltungskosten")</f>
-        <v/>
-      </c>
-      <c r="I16" s="8">
-        <f>SUMIFS('[Referenzen.xlsx]Referenzen'!$D$176:$D$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,'[Steuerung.xlsx]Steuerung'!$F$11,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,"Raumkosten")+SUMIFS('[Referenzen.xlsx]Referenzen'!$D$176:$D$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,'[Steuerung.xlsx]Steuerung'!$F$11,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,"Fuhrparkkosten")+SUMIFS('[Referenzen.xlsx]Referenzen'!$D$176:$D$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,'[Steuerung.xlsx]Steuerung'!$F$11,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,"Instandh. Betriebsausstattung")+SUMIFS('[Referenzen.xlsx]Referenzen'!$D$176:$D$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,'[Steuerung.xlsx]Steuerung'!$F$11,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,"Vertriebskosten")+SUMIFS('[Referenzen.xlsx]Referenzen'!$D$176:$D$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,'[Steuerung.xlsx]Steuerung'!$F$11,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,"Verwaltungskosten")</f>
-        <v/>
-      </c>
-      <c r="J16" s="8">
-        <f>SUMIFS('[Referenzen.xlsx]Referenzen'!$E$176:$E$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,'[Steuerung.xlsx]Steuerung'!$F$11,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,"Raumkosten")+SUMIFS('[Referenzen.xlsx]Referenzen'!$E$176:$E$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,'[Steuerung.xlsx]Steuerung'!$F$11,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,"Fuhrparkkosten")+SUMIFS('[Referenzen.xlsx]Referenzen'!$E$176:$E$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,'[Steuerung.xlsx]Steuerung'!$F$11,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,"Instandh. Betriebsausstattung")+SUMIFS('[Referenzen.xlsx]Referenzen'!$E$176:$E$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,'[Steuerung.xlsx]Steuerung'!$F$11,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,"Vertriebskosten")+SUMIFS('[Referenzen.xlsx]Referenzen'!$E$176:$E$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,'[Steuerung.xlsx]Steuerung'!$F$11,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,"Verwaltungskosten")</f>
-        <v/>
-      </c>
-      <c r="K16" s="8">
-        <f>SUMIFS('[Referenzen.xlsx]Referenzen'!$F$176:$F$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,'[Steuerung.xlsx]Steuerung'!$F$11,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,"Raumkosten")+SUMIFS('[Referenzen.xlsx]Referenzen'!$F$176:$F$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,'[Steuerung.xlsx]Steuerung'!$F$11,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,"Fuhrparkkosten")+SUMIFS('[Referenzen.xlsx]Referenzen'!$F$176:$F$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,'[Steuerung.xlsx]Steuerung'!$F$11,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,"Instandh. Betriebsausstattung")+SUMIFS('[Referenzen.xlsx]Referenzen'!$F$176:$F$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,'[Steuerung.xlsx]Steuerung'!$F$11,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,"Vertriebskosten")+SUMIFS('[Referenzen.xlsx]Referenzen'!$F$176:$F$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,'[Steuerung.xlsx]Steuerung'!$F$11,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,"Verwaltungskosten")</f>
-        <v/>
+      <c r="H16" s="8" t="n">
+        <v>994054.01</v>
+      </c>
+      <c r="I16" s="8" t="n">
+        <v>469888.56</v>
+      </c>
+      <c r="J16" s="8" t="n">
+        <v>414125.78</v>
+      </c>
+      <c r="K16" s="8" t="n">
+        <v>185582.05</v>
       </c>
       <c r="L16" s="1" t="n"/>
       <c r="M16" s="1" t="n"/>
@@ -1124,21 +1084,17 @@
           <t>Anteil Gesamtleistung</t>
         </is>
       </c>
-      <c r="H17" s="10">
-        <f>IF(SUM('[Mehrjahresplan.xlsx]Mehrjahresplan'!$D$24:$D$27)=0,"n.a.",SUMIFS('[Referenzen.xlsx]Referenzen'!$C$176:$C$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,'[Steuerung.xlsx]Steuerung'!$F$11,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,"Gesamtleistung")/SUM('[Mehrjahresplan.xlsx]Mehrjahresplan'!$D$24:$D$27))</f>
-        <v/>
-      </c>
-      <c r="I17" s="10">
-        <f>IF(SUM('[Mehrjahresplan.xlsx]Mehrjahresplan'!$D$24:$D$27)=0,"n.a.",SUMIFS('[Referenzen.xlsx]Referenzen'!$D$176:$D$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,'[Steuerung.xlsx]Steuerung'!$F$11,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,"Gesamtleistung")/SUM('[Mehrjahresplan.xlsx]Mehrjahresplan'!$D$24:$D$27))</f>
-        <v/>
-      </c>
-      <c r="J17" s="10">
-        <f>IF(SUM('[Mehrjahresplan.xlsx]Mehrjahresplan'!$D$24:$D$27)=0,"n.a.",SUMIFS('[Referenzen.xlsx]Referenzen'!$E$176:$E$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,'[Steuerung.xlsx]Steuerung'!$F$11,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,"Gesamtleistung")/SUM('[Mehrjahresplan.xlsx]Mehrjahresplan'!$D$24:$D$27))</f>
-        <v/>
-      </c>
-      <c r="K17" s="10">
-        <f>IF(SUM('[Mehrjahresplan.xlsx]Mehrjahresplan'!$D$24:$D$27)=0,"n.a.",SUMIFS('[Referenzen.xlsx]Referenzen'!$F$176:$F$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,'[Steuerung.xlsx]Steuerung'!$F$11,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,"Gesamtleistung")/SUM('[Mehrjahresplan.xlsx]Mehrjahresplan'!$D$24:$D$27))</f>
-        <v/>
+      <c r="H17" s="10" t="n">
+        <v>0.5669934640522876</v>
+      </c>
+      <c r="I17" s="10" t="n">
+        <v>0.196078431372549</v>
+      </c>
+      <c r="J17" s="10" t="n">
+        <v>0.1756535947712418</v>
+      </c>
+      <c r="K17" s="10" t="n">
+        <v>0.06127450980392157</v>
       </c>
       <c r="L17" s="1" t="n"/>
       <c r="M17" s="1" t="n"/>
@@ -1164,21 +1120,17 @@
           <t>Verwaltungsumlage</t>
         </is>
       </c>
-      <c r="H18" s="8">
-        <f>SUMIFS('[Referenzen.xlsx]Referenzen'!$G$176:$G$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,'[Steuerung.xlsx]Steuerung'!$F$11,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,"&lt;&gt;Gesamtleistung")*H17</f>
-        <v/>
-      </c>
-      <c r="I18" s="8">
-        <f>SUMIFS('[Referenzen.xlsx]Referenzen'!$G$176:$G$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,'[Steuerung.xlsx]Steuerung'!$F$11,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,"&lt;&gt;Gesamtleistung")*I17</f>
-        <v/>
-      </c>
-      <c r="J18" s="8">
-        <f>SUMIFS('[Referenzen.xlsx]Referenzen'!$G$176:$G$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,'[Steuerung.xlsx]Steuerung'!$F$11,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,"&lt;&gt;Gesamtleistung")*J17</f>
-        <v/>
-      </c>
-      <c r="K18" s="8">
-        <f>SUMIFS('[Referenzen.xlsx]Referenzen'!$G$176:$G$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,'[Steuerung.xlsx]Steuerung'!$F$11,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,"&lt;&gt;Gesamtleistung")*K17</f>
-        <v/>
+      <c r="H18" s="8" t="n">
+        <v>770633.436127451</v>
+      </c>
+      <c r="I18" s="8" t="n">
+        <v>266501.4764705882</v>
+      </c>
+      <c r="J18" s="8" t="n">
+        <v>238740.9060049019</v>
+      </c>
+      <c r="K18" s="8" t="n">
+        <v>83281.71139705883</v>
       </c>
       <c r="L18" s="1" t="n"/>
       <c r="M18" s="1" t="n"/>
@@ -1204,21 +1156,17 @@
           <t>Eigenleistungsquote</t>
         </is>
       </c>
-      <c r="H19" s="10">
-        <f>1-SUMIFS('[Referenzen.xlsx]Referenzen'!$C$176:$C$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,'[Steuerung.xlsx]Steuerung'!$F$11,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,"Vorleistungen")/SUMIFS('[Referenzen.xlsx]Referenzen'!$C$176:$C$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,'[Steuerung.xlsx]Steuerung'!$F$11,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,"Gesamtleistung")</f>
-        <v/>
-      </c>
-      <c r="I19" s="10">
-        <f>1-SUMIFS('[Referenzen.xlsx]Referenzen'!$D$176:$D$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,'[Steuerung.xlsx]Steuerung'!$F$11,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,"Vorleistungen")/SUMIFS('[Referenzen.xlsx]Referenzen'!$D$176:$D$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,'[Steuerung.xlsx]Steuerung'!$F$11,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,"Gesamtleistung")</f>
-        <v/>
-      </c>
-      <c r="J19" s="10">
-        <f>1-SUMIFS('[Referenzen.xlsx]Referenzen'!$E$176:$E$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,'[Steuerung.xlsx]Steuerung'!$F$11,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,"Vorleistungen")/SUMIFS('[Referenzen.xlsx]Referenzen'!$E$176:$E$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,'[Steuerung.xlsx]Steuerung'!$F$11,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,"Gesamtleistung")</f>
-        <v/>
-      </c>
-      <c r="K19" s="10">
-        <f>1-SUMIFS('[Referenzen.xlsx]Referenzen'!$F$176:$F$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,'[Steuerung.xlsx]Steuerung'!$F$11,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,"Vorleistungen")/SUMIFS('[Referenzen.xlsx]Referenzen'!$F$176:$F$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,'[Steuerung.xlsx]Steuerung'!$F$11,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,"Gesamtleistung")</f>
-        <v/>
+      <c r="H19" s="10" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="I19" s="10" t="n">
+        <v>0.4152083333333333</v>
+      </c>
+      <c r="J19" s="10" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="K19" s="10" t="n">
+        <v>0.41</v>
       </c>
       <c r="L19" s="1" t="n"/>
       <c r="M19" s="1" t="n"/>
@@ -1244,21 +1192,17 @@
           <t>GK auf Eigenstunden</t>
         </is>
       </c>
-      <c r="H20" s="7">
-        <f>SUM(H15:H16,H18)*H19*$D$23</f>
-        <v/>
-      </c>
-      <c r="I20" s="7">
-        <f>SUM(I15:I16,I18)*I19*$D$23</f>
-        <v/>
-      </c>
-      <c r="J20" s="7">
-        <f>SUM(J15:J16,J18)*J19*$D$23</f>
-        <v/>
-      </c>
-      <c r="K20" s="7">
-        <f>SUM(K15:K16,K18)*K19*$D$23</f>
-        <v/>
+      <c r="H20" s="7" t="n">
+        <v>910754.1200216149</v>
+      </c>
+      <c r="I20" s="7" t="n">
+        <v>479647.1624085497</v>
+      </c>
+      <c r="J20" s="7" t="n">
+        <v>470284.5696335422</v>
+      </c>
+      <c r="K20" s="7" t="n">
+        <v>202676.5816141271</v>
       </c>
       <c r="L20" s="1" t="n"/>
       <c r="M20" s="1" t="n"/>
@@ -1284,21 +1228,17 @@
           <t>Gemeinkostensatz</t>
         </is>
       </c>
-      <c r="H21" s="7">
-        <f>IF(H9=0,"n.a.",H20/H9)</f>
-        <v/>
-      </c>
-      <c r="I21" s="7">
-        <f>IF(I9=0,"n.a.",I20/I9)</f>
-        <v/>
-      </c>
-      <c r="J21" s="7">
-        <f>IF(J9=0,"n.a.",J20/J9)</f>
-        <v/>
-      </c>
-      <c r="K21" s="7">
-        <f>IF(K9=0,"n.a.",K20/K9)</f>
-        <v/>
+      <c r="H21" s="7" t="n">
+        <v>61.48534193232862</v>
+      </c>
+      <c r="I21" s="7" t="n">
+        <v>28.06071804973111</v>
+      </c>
+      <c r="J21" s="7" t="n">
+        <v>31.74908236344854</v>
+      </c>
+      <c r="K21" s="7" t="n">
+        <v>50.1701557463786</v>
       </c>
       <c r="L21" s="1" t="n"/>
       <c r="M21" s="1" t="n"/>
@@ -1324,21 +1264,17 @@
           <t>Vollkostensatz</t>
         </is>
       </c>
-      <c r="H22" s="12">
-        <f>H13+H21</f>
-        <v/>
-      </c>
-      <c r="I22" s="12">
-        <f>I13+I21</f>
-        <v/>
-      </c>
-      <c r="J22" s="12">
-        <f>J13+J21</f>
-        <v/>
-      </c>
-      <c r="K22" s="12">
-        <f>K13+K21</f>
-        <v/>
+      <c r="H22" s="12" t="n">
+        <v>108.9843390918145</v>
+      </c>
+      <c r="I22" s="12" t="n">
+        <v>67.91247724052315</v>
+      </c>
+      <c r="J22" s="12" t="n">
+        <v>74.06668133289995</v>
+      </c>
+      <c r="K22" s="12" t="n">
+        <v>90.89774026943928</v>
       </c>
       <c r="L22" s="1" t="n"/>
       <c r="M22" s="1" t="n"/>
@@ -1364,21 +1300,17 @@
           <t>Planmarge</t>
         </is>
       </c>
-      <c r="H23" s="10">
-        <f>(SUMIFS('[Referenzen.xlsx]Referenzen'!$C$176:$C$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,'[Steuerung.xlsx]Steuerung'!$F$11,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,"Gesamtleistung")-SUMIFS('[Referenzen.xlsx]Referenzen'!$C$176:$C$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,'[Steuerung.xlsx]Steuerung'!$F$11,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,"&lt;&gt;Gesamtleistung"))/SUMIFS('[Referenzen.xlsx]Referenzen'!$C$176:$C$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,'[Steuerung.xlsx]Steuerung'!$F$11,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,"Gesamtleistung")</f>
-        <v/>
-      </c>
-      <c r="I23" s="10">
-        <f>(SUMIFS('[Referenzen.xlsx]Referenzen'!$D$176:$D$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,'[Steuerung.xlsx]Steuerung'!$F$11,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,"Gesamtleistung")-SUMIFS('[Referenzen.xlsx]Referenzen'!$D$176:$D$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,'[Steuerung.xlsx]Steuerung'!$F$11,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,"&lt;&gt;Gesamtleistung"))/SUMIFS('[Referenzen.xlsx]Referenzen'!$D$176:$D$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,'[Steuerung.xlsx]Steuerung'!$F$11,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,"Gesamtleistung")</f>
-        <v/>
-      </c>
-      <c r="J23" s="10">
-        <f>(SUMIFS('[Referenzen.xlsx]Referenzen'!$E$176:$E$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,'[Steuerung.xlsx]Steuerung'!$F$11,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,"Gesamtleistung")-SUMIFS('[Referenzen.xlsx]Referenzen'!$E$176:$E$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,'[Steuerung.xlsx]Steuerung'!$F$11,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,"&lt;&gt;Gesamtleistung"))/SUMIFS('[Referenzen.xlsx]Referenzen'!$E$176:$E$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,'[Steuerung.xlsx]Steuerung'!$F$11,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,"Gesamtleistung")</f>
-        <v/>
-      </c>
-      <c r="K23" s="10">
-        <f>(SUMIFS('[Referenzen.xlsx]Referenzen'!$F$176:$F$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,'[Steuerung.xlsx]Steuerung'!$F$11,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,"Gesamtleistung")-SUMIFS('[Referenzen.xlsx]Referenzen'!$F$176:$F$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,'[Steuerung.xlsx]Steuerung'!$F$11,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,"&lt;&gt;Gesamtleistung"))/SUMIFS('[Referenzen.xlsx]Referenzen'!$F$176:$F$215,'[Referenzen.xlsx]Referenzen'!$A$176:$A$215,'[Steuerung.xlsx]Steuerung'!$F$11,'[Referenzen.xlsx]Referenzen'!$B$176:$B$215,"Gesamtleistung")</f>
-        <v/>
+      <c r="H23" s="10" t="n">
+        <v>0.1197799704610951</v>
+      </c>
+      <c r="I23" s="10" t="n">
+        <v>0.08814821666666675</v>
+      </c>
+      <c r="J23" s="10" t="n">
+        <v>0.05299400465116284</v>
+      </c>
+      <c r="K23" s="10" t="n">
+        <v>0.0262786333333333</v>
       </c>
       <c r="L23" s="1" t="n"/>
       <c r="M23" s="1" t="n"/>
@@ -1398,21 +1330,17 @@
           <t>Angebotssatz</t>
         </is>
       </c>
-      <c r="H24" s="12">
-        <f>IF(H23&gt;=1,"n.a.",H22/(1-H23))</f>
-        <v/>
-      </c>
-      <c r="I24" s="12">
-        <f>IF(I23&gt;=1,"n.a.",I22/(1-I23))</f>
-        <v/>
-      </c>
-      <c r="J24" s="12">
-        <f>IF(J23&gt;=1,"n.a.",J22/(1-J23))</f>
-        <v/>
-      </c>
-      <c r="K24" s="12">
-        <f>IF(K23&gt;=1,"n.a.",K22/(1-K23))</f>
-        <v/>
+      <c r="H24" s="12" t="n">
+        <v>123.8148820004754</v>
+      </c>
+      <c r="I24" s="12" t="n">
+        <v>74.47753953198917</v>
+      </c>
+      <c r="J24" s="12" t="n">
+        <v>78.21141755878421</v>
+      </c>
+      <c r="K24" s="12" t="n">
+        <v>93.35087364941869</v>
       </c>
       <c r="L24" s="1" t="n"/>
       <c r="M24" s="1" t="n"/>
@@ -1428,9 +1356,8 @@
           <t>Produktivitätsgrad</t>
         </is>
       </c>
-      <c r="D25" s="13">
-        <f>($D$9-$D$10-$D$11-$D$12)/$D$9</f>
-        <v/>
+      <c r="D25" s="13" t="n">
+        <v>0.6486486486486487</v>
       </c>
       <c r="E25" s="1" t="n"/>
       <c r="F25" s="1" t="n"/>
@@ -1561,9 +1488,8 @@
           <t>Vertragsarbeitstage</t>
         </is>
       </c>
-      <c r="H31" s="7">
-        <f>D31-D32-D33</f>
-        <v/>
+      <c r="H31" s="7" t="n">
+        <v>252</v>
       </c>
       <c r="I31" s="1" t="n"/>
       <c r="J31" s="1" t="n"/>
@@ -1592,9 +1518,8 @@
           <t>Anwesenheitstage</t>
         </is>
       </c>
-      <c r="H32" s="7">
-        <f>H31-D34-D35</f>
-        <v/>
+      <c r="H32" s="7" t="n">
+        <v>212</v>
       </c>
       <c r="I32" s="1" t="n"/>
       <c r="J32" s="1" t="n"/>
@@ -1623,9 +1548,8 @@
           <t>Arbeitsstunden / Jahr</t>
         </is>
       </c>
-      <c r="H33" s="7">
-        <f>H32*D36</f>
-        <v/>
+      <c r="H33" s="7" t="n">
+        <v>1696</v>
       </c>
       <c r="I33" s="1" t="n"/>
       <c r="J33" s="1" t="n"/>
@@ -1654,9 +1578,8 @@
           <t>Anwesenheit brutto</t>
         </is>
       </c>
-      <c r="H34" s="7">
-        <f>H33+D37*12</f>
-        <v/>
+      <c r="H34" s="7" t="n">
+        <v>1816</v>
       </c>
       <c r="I34" s="1" t="n"/>
       <c r="J34" s="1" t="n"/>
@@ -1685,9 +1608,8 @@
           <t>Produktive Stunden</t>
         </is>
       </c>
-      <c r="H35" s="7">
-        <f>H34-D38-H33*D39</f>
-        <v/>
+      <c r="H35" s="7" t="n">
+        <v>1476.8</v>
       </c>
       <c r="I35" s="1" t="n"/>
       <c r="J35" s="1" t="n"/>
@@ -1716,9 +1638,8 @@
           <t>Monatslohn</t>
         </is>
       </c>
-      <c r="H36" s="7">
-        <f>D40*180</f>
-        <v/>
+      <c r="H36" s="7" t="n">
+        <v>3150</v>
       </c>
       <c r="I36" s="1" t="n"/>
       <c r="J36" s="1" t="n"/>
@@ -1747,9 +1668,8 @@
           <t>AG-Sozialversicherung</t>
         </is>
       </c>
-      <c r="H37" s="7">
-        <f>H36*D41</f>
-        <v/>
+      <c r="H37" s="7" t="n">
+        <v>630</v>
       </c>
       <c r="I37" s="1" t="n"/>
       <c r="J37" s="1" t="n"/>
@@ -1778,9 +1698,8 @@
           <t>Urlaubsgeld</t>
         </is>
       </c>
-      <c r="H38" s="7">
-        <f>D40*170*D42</f>
-        <v/>
+      <c r="H38" s="7" t="n">
+        <v>1487.5</v>
       </c>
       <c r="I38" s="1" t="n"/>
       <c r="J38" s="1" t="n"/>
@@ -1809,9 +1728,8 @@
           <t>Weihnachtsgeld</t>
         </is>
       </c>
-      <c r="H39" s="7">
-        <f>D40*170*D43</f>
-        <v/>
+      <c r="H39" s="7" t="n">
+        <v>1487.5</v>
       </c>
       <c r="I39" s="1" t="n"/>
       <c r="J39" s="1" t="n"/>
@@ -1840,9 +1758,8 @@
           <t>Jahresbasis</t>
         </is>
       </c>
-      <c r="H40" s="7">
-        <f>12*(H36+H37+D44)+H38+H39</f>
-        <v/>
+      <c r="H40" s="7" t="n">
+        <v>48959</v>
       </c>
       <c r="I40" s="1" t="n"/>
       <c r="J40" s="1" t="n"/>
@@ -1871,9 +1788,8 @@
           <t>Jahresaufwand</t>
         </is>
       </c>
-      <c r="H41" s="7">
-        <f>H40*(1+D45+D46)</f>
-        <v/>
+      <c r="H41" s="7" t="n">
+        <v>50917.36</v>
       </c>
       <c r="I41" s="1" t="n"/>
       <c r="J41" s="1" t="n"/>
@@ -1902,9 +1818,8 @@
           <t>Satz ohne Verwaltungs-GK</t>
         </is>
       </c>
-      <c r="H42" s="12">
-        <f>IF(H35=0,"n.a.",H41/H35)</f>
-        <v/>
+      <c r="H42" s="12" t="n">
+        <v>34.47816901408451</v>
       </c>
       <c r="I42" s="1" t="n"/>
       <c r="J42" s="1" t="n"/>
@@ -1933,9 +1848,8 @@
           <t>Satz mit Verwaltungs-GK</t>
         </is>
       </c>
-      <c r="H43" s="16">
-        <f>H42*(1+D47+D48)</f>
-        <v/>
+      <c r="H43" s="16" t="n">
+        <v>48.959</v>
       </c>
       <c r="I43" s="1" t="n"/>
       <c r="J43" s="1" t="n"/>
@@ -2265,13 +2179,11 @@
       <c r="G65" s="6" t="n">
         <v>2863.75</v>
       </c>
-      <c r="H65" s="7">
-        <f>F65*IF(E65,$D$8,$D$7)*12</f>
-        <v/>
-      </c>
-      <c r="I65" s="7">
-        <f>F65*G65*12</f>
-        <v/>
+      <c r="H65" s="7" t="n">
+        <v>4152</v>
+      </c>
+      <c r="I65" s="7" t="n">
+        <v>68730</v>
       </c>
     </row>
     <row r="66">
@@ -2294,13 +2206,11 @@
       <c r="G66" s="6" t="n">
         <v>3950</v>
       </c>
-      <c r="H66" s="7">
-        <f>F66*IF(E66,$D$8,$D$7)*12</f>
-        <v/>
-      </c>
-      <c r="I66" s="7">
-        <f>F66*G66*12</f>
-        <v/>
+      <c r="H66" s="7" t="n">
+        <v>2076</v>
+      </c>
+      <c r="I66" s="7" t="n">
+        <v>47400</v>
       </c>
     </row>
     <row r="67">
@@ -2323,13 +2233,11 @@
       <c r="G67" s="6" t="n">
         <v>2950</v>
       </c>
-      <c r="H67" s="7">
-        <f>F67*IF(E67,$D$8,$D$7)*12</f>
-        <v/>
-      </c>
-      <c r="I67" s="7">
-        <f>F67*G67*12</f>
-        <v/>
+      <c r="H67" s="7" t="n">
+        <v>4152</v>
+      </c>
+      <c r="I67" s="7" t="n">
+        <v>70800</v>
       </c>
     </row>
     <row r="68">
@@ -2352,13 +2260,11 @@
       <c r="G68" s="6" t="n">
         <v>3950</v>
       </c>
-      <c r="H68" s="7">
-        <f>F68*IF(E68,$D$8,$D$7)*12</f>
-        <v/>
-      </c>
-      <c r="I68" s="7">
-        <f>F68*G68*12</f>
-        <v/>
+      <c r="H68" s="7" t="n">
+        <v>8304</v>
+      </c>
+      <c r="I68" s="7" t="n">
+        <v>189600</v>
       </c>
     </row>
     <row r="69">
@@ -2381,13 +2287,11 @@
       <c r="G69" s="6" t="n">
         <v>3015.25</v>
       </c>
-      <c r="H69" s="7">
-        <f>F69*IF(E69,$D$8,$D$7)*12</f>
-        <v/>
-      </c>
-      <c r="I69" s="7">
-        <f>F69*G69*12</f>
-        <v/>
+      <c r="H69" s="7" t="n">
+        <v>6228</v>
+      </c>
+      <c r="I69" s="7" t="n">
+        <v>108549</v>
       </c>
     </row>
     <row r="70">
@@ -2410,13 +2314,11 @@
       <c r="G70" s="6" t="n">
         <v>3069.68</v>
       </c>
-      <c r="H70" s="7">
-        <f>F70*IF(E70,$D$8,$D$7)*12</f>
-        <v/>
-      </c>
-      <c r="I70" s="7">
-        <f>F70*G70*12</f>
-        <v/>
+      <c r="H70" s="7" t="n">
+        <v>4152</v>
+      </c>
+      <c r="I70" s="7" t="n">
+        <v>73672.31999999999</v>
       </c>
     </row>
     <row r="71">
@@ -2439,13 +2341,11 @@
       <c r="G71" s="6" t="n">
         <v>2988.14</v>
       </c>
-      <c r="H71" s="7">
-        <f>F71*IF(E71,$D$8,$D$7)*12</f>
-        <v/>
-      </c>
-      <c r="I71" s="7">
-        <f>F71*G71*12</f>
-        <v/>
+      <c r="H71" s="7" t="n">
+        <v>16608</v>
+      </c>
+      <c r="I71" s="7" t="n">
+        <v>286861.44</v>
       </c>
     </row>
     <row r="72">
@@ -2468,13 +2368,11 @@
       <c r="G72" s="6" t="n">
         <v>556</v>
       </c>
-      <c r="H72" s="7">
-        <f>F72*IF(E72,$D$8,$D$7)*12</f>
-        <v/>
-      </c>
-      <c r="I72" s="7">
-        <f>F72*G72*12</f>
-        <v/>
+      <c r="H72" s="7" t="n">
+        <v>1440</v>
+      </c>
+      <c r="I72" s="7" t="n">
+        <v>20016</v>
       </c>
     </row>
     <row r="73">
@@ -2497,13 +2395,11 @@
       <c r="G73" s="6" t="n">
         <v>3600</v>
       </c>
-      <c r="H73" s="7">
-        <f>F73*IF(E73,$D$8,$D$7)*12</f>
-        <v/>
-      </c>
-      <c r="I73" s="7">
-        <f>F73*G73*12</f>
-        <v/>
+      <c r="H73" s="7" t="n">
+        <v>8304</v>
+      </c>
+      <c r="I73" s="7" t="n">
+        <v>172800</v>
       </c>
     </row>
     <row r="74">
@@ -2526,13 +2422,11 @@
       <c r="G74" s="6" t="n">
         <v>3019.93</v>
       </c>
-      <c r="H74" s="7">
-        <f>F74*IF(E74,$D$8,$D$7)*12</f>
-        <v/>
-      </c>
-      <c r="I74" s="7">
-        <f>F74*G74*12</f>
-        <v/>
+      <c r="H74" s="7" t="n">
+        <v>4152</v>
+      </c>
+      <c r="I74" s="7" t="n">
+        <v>72478.31999999999</v>
       </c>
     </row>
     <row r="75">
@@ -2555,13 +2449,11 @@
       <c r="G75" s="6" t="n">
         <v>3981.86</v>
       </c>
-      <c r="H75" s="7">
-        <f>F75*IF(E75,$D$8,$D$7)*12</f>
-        <v/>
-      </c>
-      <c r="I75" s="7">
-        <f>F75*G75*12</f>
-        <v/>
+      <c r="H75" s="7" t="n">
+        <v>14532</v>
+      </c>
+      <c r="I75" s="7" t="n">
+        <v>334476.24</v>
       </c>
     </row>
     <row r="76">
@@ -2584,15 +2476,15 @@
       <c r="G76" s="6" t="n">
         <v>3768.75</v>
       </c>
-      <c r="H76" s="7">
-        <f>F76*IF(E76,$D$8,$D$7)*12</f>
-        <v/>
-      </c>
-      <c r="I76" s="7">
-        <f>F76*G76*12</f>
-        <v/>
-      </c>
-    </row>
+      <c r="H76" s="7" t="n">
+        <v>4152</v>
+      </c>
+      <c r="I76" s="7" t="n">
+        <v>90450</v>
+      </c>
+    </row>
+    <row r="77"/>
+    <row r="78"/>
     <row r="79">
       <c r="C79" t="inlineStr">
         <is>
